--- a/HCM/HCM_Requirement testcase.xlsx
+++ b/HCM/HCM_Requirement testcase.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Excel documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Excel documents\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4DE6F4-7F48-4CF6-9166-AC609607772D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12452649-A91C-466F-B90C-A20A419EC14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HCM_Test_Cases" sheetId="1" r:id="rId1"/>
-    <sheet name="HCM- interview master Testcase " sheetId="2" r:id="rId2"/>
+    <sheet name="HCM- interview Requirment scre " sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -5358,7 +5358,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5381,27 +5402,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5968,10 +5968,10 @@
       <c r="J10" s="3"/>
     </row>
     <row r="13" spans="1:10" ht="21" x14ac:dyDescent="0.5">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="18" t="s">
         <v>1084</v>
       </c>
-      <c r="B13" s="13"/>
+      <c r="B13" s="18"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
@@ -6097,10 +6097,10 @@
       <c r="B20" s="2"/>
     </row>
     <row r="21" spans="1:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="18" t="s">
         <v>1085</v>
       </c>
-      <c r="B21" s="13"/>
+      <c r="B21" s="18"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
@@ -6282,12 +6282,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="17"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -7832,11 +7832,11 @@
       </c>
     </row>
     <row r="56" spans="1:9" ht="51.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="22" t="s">
         <v>349</v>
       </c>
-      <c r="B56" s="16"/>
-      <c r="C56" s="17"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="24"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -8192,7 +8192,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
         <v>394</v>
       </c>
@@ -8366,7 +8366,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="8" t="s">
         <v>419</v>
       </c>
@@ -8424,7 +8424,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
         <v>426</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
         <v>442</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="8" t="s">
         <v>453</v>
       </c>
@@ -9585,11 +9585,11 @@
       </c>
     </row>
     <row r="118" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="18" t="s">
+      <c r="A118" s="25" t="s">
         <v>573</v>
       </c>
-      <c r="B118" s="18"/>
-      <c r="C118" s="18"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="25"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
@@ -10787,11 +10787,11 @@
       </c>
     </row>
     <row r="161" spans="1:9" ht="53.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="15" t="s">
+      <c r="A161" s="22" t="s">
         <v>673</v>
       </c>
-      <c r="B161" s="16"/>
-      <c r="C161" s="17"/>
+      <c r="B161" s="23"/>
+      <c r="C161" s="24"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
@@ -11989,11 +11989,11 @@
       </c>
     </row>
     <row r="204" spans="1:9" ht="50.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A204" s="19" t="s">
+      <c r="A204" s="26" t="s">
         <v>768</v>
       </c>
-      <c r="B204" s="20"/>
-      <c r="C204" s="21"/>
+      <c r="B204" s="27"/>
+      <c r="C204" s="28"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
@@ -13771,11 +13771,11 @@
       </c>
     </row>
     <row r="267" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="15" t="s">
+      <c r="A267" s="22" t="s">
         <v>895</v>
       </c>
-      <c r="B267" s="16"/>
-      <c r="C267" s="17"/>
+      <c r="B267" s="23"/>
+      <c r="C267" s="24"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
       <c r="F267" s="3"/>
@@ -15321,11 +15321,11 @@
       </c>
     </row>
     <row r="322" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A322" s="14" t="s">
+      <c r="A322" s="21" t="s">
         <v>998</v>
       </c>
-      <c r="B322" s="14"/>
-      <c r="C322" s="14"/>
+      <c r="B322" s="21"/>
+      <c r="C322" s="21"/>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
       <c r="F322" s="3"/>
@@ -16842,914 +16842,914 @@
       </c>
     </row>
     <row r="377" spans="1:9" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A377" s="14" t="s">
+      <c r="A377" s="21" t="s">
         <v>1205</v>
       </c>
-      <c r="B377" s="14"/>
-      <c r="C377" s="14"/>
+      <c r="B377" s="21"/>
+      <c r="C377" s="21"/>
     </row>
     <row r="378" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A378" s="22" t="s">
+      <c r="A378" s="13" t="s">
         <v>896</v>
       </c>
-      <c r="B378" s="22" t="s">
+      <c r="B378" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C378" s="22" t="s">
+      <c r="C378" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D378" s="22" t="s">
+      <c r="D378" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E378" s="22" t="s">
+      <c r="E378" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="F378" s="22" t="s">
+      <c r="F378" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="G378" s="22" t="s">
+      <c r="G378" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="H378" s="22" t="s">
+      <c r="H378" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I378" s="22" t="s">
+      <c r="I378" s="13" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="379" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A379" s="23" t="s">
+      <c r="A379" s="14" t="s">
         <v>1086</v>
       </c>
-      <c r="B379" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C379" s="23" t="s">
+      <c r="B379" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C379" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D379" s="23" t="s">
+      <c r="D379" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="E379" s="23" t="s">
+      <c r="E379" s="14" t="s">
         <v>1088</v>
       </c>
-      <c r="F379" s="23" t="s">
+      <c r="F379" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="G379" s="23" t="s">
+      <c r="G379" s="14" t="s">
         <v>1089</v>
       </c>
-      <c r="H379" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I379" s="23" t="s">
+      <c r="H379" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I379" s="14" t="s">
         <v>1090</v>
       </c>
     </row>
     <row r="380" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A380" s="23" t="s">
+      <c r="A380" s="14" t="s">
         <v>1091</v>
       </c>
-      <c r="B380" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C380" s="23" t="s">
+      <c r="B380" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C380" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D380" s="23" t="s">
+      <c r="D380" s="14" t="s">
         <v>1092</v>
       </c>
-      <c r="E380" s="23" t="s">
+      <c r="E380" s="14" t="s">
         <v>1093</v>
       </c>
-      <c r="F380" s="23" t="s">
+      <c r="F380" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G380" s="23" t="s">
+      <c r="G380" s="14" t="s">
         <v>1095</v>
       </c>
-      <c r="H380" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I380" s="23" t="s">
+      <c r="H380" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I380" s="14" t="s">
         <v>1096</v>
       </c>
     </row>
     <row r="381" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A381" s="23" t="s">
+      <c r="A381" s="14" t="s">
         <v>1097</v>
       </c>
-      <c r="B381" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C381" s="23" t="s">
+      <c r="B381" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C381" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D381" s="23" t="s">
+      <c r="D381" s="14" t="s">
         <v>1092</v>
       </c>
-      <c r="E381" s="23" t="s">
+      <c r="E381" s="14" t="s">
         <v>1098</v>
       </c>
-      <c r="F381" s="23" t="s">
+      <c r="F381" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G381" s="23" t="s">
+      <c r="G381" s="14" t="s">
         <v>1095</v>
       </c>
-      <c r="H381" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I381" s="23" t="s">
+      <c r="H381" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I381" s="14" t="s">
         <v>1099</v>
       </c>
     </row>
     <row r="382" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A382" s="23" t="s">
+      <c r="A382" s="14" t="s">
         <v>1100</v>
       </c>
-      <c r="B382" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C382" s="23" t="s">
+      <c r="B382" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C382" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D382" s="23" t="s">
+      <c r="D382" s="14" t="s">
         <v>1092</v>
       </c>
-      <c r="E382" s="23" t="s">
+      <c r="E382" s="14" t="s">
         <v>1101</v>
       </c>
-      <c r="F382" s="23" t="s">
+      <c r="F382" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G382" s="23" t="s">
+      <c r="G382" s="14" t="s">
         <v>1095</v>
       </c>
-      <c r="H382" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I382" s="23" t="s">
+      <c r="H382" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I382" s="14" t="s">
         <v>1102</v>
       </c>
     </row>
     <row r="383" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A383" s="23" t="s">
+      <c r="A383" s="14" t="s">
         <v>1103</v>
       </c>
-      <c r="B383" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C383" s="23" t="s">
+      <c r="B383" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C383" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D383" s="23" t="s">
+      <c r="D383" s="14" t="s">
         <v>1092</v>
       </c>
-      <c r="E383" s="23" t="s">
+      <c r="E383" s="14" t="s">
         <v>1104</v>
       </c>
-      <c r="F383" s="23" t="s">
+      <c r="F383" s="14" t="s">
         <v>1105</v>
       </c>
-      <c r="G383" s="23" t="s">
+      <c r="G383" s="14" t="s">
         <v>1106</v>
       </c>
-      <c r="H383" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I383" s="23" t="s">
+      <c r="H383" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I383" s="14" t="s">
         <v>1107</v>
       </c>
     </row>
     <row r="384" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A384" s="23" t="s">
+      <c r="A384" s="14" t="s">
         <v>1108</v>
       </c>
-      <c r="B384" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C384" s="23" t="s">
+      <c r="B384" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C384" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D384" s="23" t="s">
+      <c r="D384" s="14" t="s">
         <v>1109</v>
       </c>
-      <c r="E384" s="23" t="s">
+      <c r="E384" s="14" t="s">
         <v>1110</v>
       </c>
-      <c r="F384" s="23" t="s">
+      <c r="F384" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G384" s="23" t="s">
+      <c r="G384" s="14" t="s">
         <v>1111</v>
       </c>
-      <c r="H384" s="23" t="s">
+      <c r="H384" s="14" t="s">
         <v>1112</v>
       </c>
-      <c r="I384" s="23" t="s">
+      <c r="I384" s="14" t="s">
         <v>1113</v>
       </c>
     </row>
     <row r="385" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A385" s="23" t="s">
+      <c r="A385" s="14" t="s">
         <v>1114</v>
       </c>
-      <c r="B385" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C385" s="23" t="s">
+      <c r="B385" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C385" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D385" s="23" t="s">
+      <c r="D385" s="14" t="s">
         <v>1109</v>
       </c>
-      <c r="E385" s="23" t="s">
+      <c r="E385" s="14" t="s">
         <v>1115</v>
       </c>
-      <c r="F385" s="23" t="s">
+      <c r="F385" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G385" s="23" t="s">
+      <c r="G385" s="14" t="s">
         <v>1116</v>
       </c>
-      <c r="H385" s="23" t="s">
+      <c r="H385" s="14" t="s">
         <v>1117</v>
       </c>
-      <c r="I385" s="23" t="s">
+      <c r="I385" s="14" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="386" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A386" s="23" t="s">
+      <c r="A386" s="14" t="s">
         <v>1118</v>
       </c>
-      <c r="B386" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C386" s="23" t="s">
+      <c r="B386" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C386" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D386" s="23" t="s">
+      <c r="D386" s="14" t="s">
         <v>1109</v>
       </c>
-      <c r="E386" s="23" t="s">
+      <c r="E386" s="14" t="s">
         <v>1119</v>
       </c>
-      <c r="F386" s="23" t="s">
+      <c r="F386" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G386" s="23" t="s">
+      <c r="G386" s="14" t="s">
         <v>1120</v>
       </c>
-      <c r="H386" s="24">
+      <c r="H386" s="15">
         <v>46096</v>
       </c>
-      <c r="I386" s="23" t="s">
+      <c r="I386" s="14" t="s">
         <v>1121</v>
       </c>
     </row>
     <row r="387" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A387" s="23" t="s">
+      <c r="A387" s="14" t="s">
         <v>1122</v>
       </c>
-      <c r="B387" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C387" s="23" t="s">
+      <c r="B387" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C387" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D387" s="23" t="s">
+      <c r="D387" s="14" t="s">
         <v>1109</v>
       </c>
-      <c r="E387" s="23" t="s">
+      <c r="E387" s="14" t="s">
         <v>1123</v>
       </c>
-      <c r="F387" s="23" t="s">
+      <c r="F387" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G387" s="23" t="s">
+      <c r="G387" s="14" t="s">
         <v>1124</v>
       </c>
-      <c r="H387" s="23" t="s">
+      <c r="H387" s="14" t="s">
         <v>1125</v>
       </c>
-      <c r="I387" s="23" t="s">
+      <c r="I387" s="14" t="s">
         <v>1126</v>
       </c>
     </row>
     <row r="388" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A388" s="23" t="s">
+      <c r="A388" s="14" t="s">
         <v>1127</v>
       </c>
-      <c r="B388" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C388" s="23" t="s">
+      <c r="B388" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C388" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D388" s="23" t="s">
+      <c r="D388" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="E388" s="23" t="s">
+      <c r="E388" s="14" t="s">
         <v>1129</v>
       </c>
-      <c r="F388" s="23" t="s">
+      <c r="F388" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G388" s="23" t="s">
+      <c r="G388" s="14" t="s">
         <v>1130</v>
       </c>
-      <c r="H388" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I388" s="23" t="s">
+      <c r="H388" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I388" s="14" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="389" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A389" s="23" t="s">
+      <c r="A389" s="14" t="s">
         <v>1132</v>
       </c>
-      <c r="B389" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C389" s="23" t="s">
+      <c r="B389" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C389" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D389" s="23" t="s">
+      <c r="D389" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="E389" s="23" t="s">
+      <c r="E389" s="14" t="s">
         <v>1133</v>
       </c>
-      <c r="F389" s="23" t="s">
+      <c r="F389" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G389" s="23" t="s">
+      <c r="G389" s="14" t="s">
         <v>1134</v>
       </c>
-      <c r="H389" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I389" s="23" t="s">
+      <c r="H389" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I389" s="14" t="s">
         <v>1135</v>
       </c>
     </row>
     <row r="390" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A390" s="23" t="s">
+      <c r="A390" s="14" t="s">
         <v>1136</v>
       </c>
-      <c r="B390" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C390" s="23" t="s">
+      <c r="B390" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C390" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D390" s="23" t="s">
+      <c r="D390" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="E390" s="23" t="s">
+      <c r="E390" s="14" t="s">
         <v>635</v>
       </c>
-      <c r="F390" s="23" t="s">
+      <c r="F390" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G390" s="23" t="s">
+      <c r="G390" s="14" t="s">
         <v>1137</v>
       </c>
-      <c r="H390" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I390" s="23" t="s">
+      <c r="H390" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I390" s="14" t="s">
         <v>1138</v>
       </c>
     </row>
     <row r="391" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A391" s="23" t="s">
+      <c r="A391" s="14" t="s">
         <v>1139</v>
       </c>
-      <c r="B391" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C391" s="23" t="s">
+      <c r="B391" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C391" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D391" s="23" t="s">
+      <c r="D391" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="E391" s="23" t="s">
+      <c r="E391" s="14" t="s">
         <v>1140</v>
       </c>
-      <c r="F391" s="23" t="s">
+      <c r="F391" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G391" s="23" t="s">
+      <c r="G391" s="14" t="s">
         <v>1141</v>
       </c>
-      <c r="H391" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I391" s="23" t="s">
+      <c r="H391" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I391" s="14" t="s">
         <v>1096</v>
       </c>
     </row>
     <row r="392" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A392" s="23" t="s">
+      <c r="A392" s="14" t="s">
         <v>1142</v>
       </c>
-      <c r="B392" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C392" s="23" t="s">
+      <c r="B392" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C392" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D392" s="23" t="s">
+      <c r="D392" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="E392" s="23" t="s">
+      <c r="E392" s="14" t="s">
         <v>1143</v>
       </c>
-      <c r="F392" s="23" t="s">
+      <c r="F392" s="14" t="s">
         <v>493</v>
       </c>
-      <c r="G392" s="23" t="s">
+      <c r="G392" s="14" t="s">
         <v>1144</v>
       </c>
-      <c r="H392" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I392" s="23" t="s">
+      <c r="H392" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I392" s="14" t="s">
         <v>1145</v>
       </c>
     </row>
     <row r="393" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A393" s="23" t="s">
+      <c r="A393" s="14" t="s">
         <v>1146</v>
       </c>
-      <c r="B393" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C393" s="23" t="s">
+      <c r="B393" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C393" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D393" s="23" t="s">
+      <c r="D393" s="14" t="s">
         <v>1147</v>
       </c>
-      <c r="E393" s="23" t="s">
+      <c r="E393" s="14" t="s">
         <v>1110</v>
       </c>
-      <c r="F393" s="23" t="s">
+      <c r="F393" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G393" s="23" t="s">
+      <c r="G393" s="14" t="s">
         <v>1148</v>
       </c>
-      <c r="H393" s="23" t="s">
+      <c r="H393" s="14" t="s">
         <v>1112</v>
       </c>
-      <c r="I393" s="23" t="s">
+      <c r="I393" s="14" t="s">
         <v>1113</v>
       </c>
     </row>
     <row r="394" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A394" s="23" t="s">
+      <c r="A394" s="14" t="s">
         <v>1149</v>
       </c>
-      <c r="B394" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C394" s="23" t="s">
+      <c r="B394" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C394" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D394" s="23" t="s">
+      <c r="D394" s="14" t="s">
         <v>1147</v>
       </c>
-      <c r="E394" s="23" t="s">
+      <c r="E394" s="14" t="s">
         <v>1150</v>
       </c>
-      <c r="F394" s="23" t="s">
+      <c r="F394" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G394" s="23" t="s">
+      <c r="G394" s="14" t="s">
         <v>1116</v>
       </c>
-      <c r="H394" s="23" t="s">
+      <c r="H394" s="14" t="s">
         <v>1117</v>
       </c>
-      <c r="I394" s="23" t="s">
+      <c r="I394" s="14" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="395" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A395" s="23" t="s">
+      <c r="A395" s="14" t="s">
         <v>1151</v>
       </c>
-      <c r="B395" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C395" s="23" t="s">
+      <c r="B395" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C395" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D395" s="23" t="s">
+      <c r="D395" s="14" t="s">
         <v>1152</v>
       </c>
-      <c r="E395" s="23" t="s">
+      <c r="E395" s="14" t="s">
         <v>1129</v>
       </c>
-      <c r="F395" s="23" t="s">
+      <c r="F395" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G395" s="23" t="s">
+      <c r="G395" s="14" t="s">
         <v>1130</v>
       </c>
-      <c r="H395" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I395" s="23" t="s">
+      <c r="H395" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I395" s="14" t="s">
         <v>1153</v>
       </c>
     </row>
     <row r="396" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A396" s="23" t="s">
+      <c r="A396" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="B396" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C396" s="23" t="s">
+      <c r="B396" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C396" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D396" s="23" t="s">
+      <c r="D396" s="14" t="s">
         <v>1152</v>
       </c>
-      <c r="E396" s="23" t="s">
+      <c r="E396" s="14" t="s">
         <v>1155</v>
       </c>
-      <c r="F396" s="23" t="s">
+      <c r="F396" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G396" s="23" t="s">
+      <c r="G396" s="14" t="s">
         <v>1134</v>
       </c>
-      <c r="H396" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I396" s="23" t="s">
+      <c r="H396" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I396" s="14" t="s">
         <v>1156</v>
       </c>
     </row>
     <row r="397" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A397" s="23" t="s">
+      <c r="A397" s="14" t="s">
         <v>1157</v>
       </c>
-      <c r="B397" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C397" s="23" t="s">
+      <c r="B397" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C397" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D397" s="23" t="s">
+      <c r="D397" s="14" t="s">
         <v>1152</v>
       </c>
-      <c r="E397" s="23" t="s">
+      <c r="E397" s="14" t="s">
         <v>635</v>
       </c>
-      <c r="F397" s="23" t="s">
+      <c r="F397" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G397" s="23" t="s">
+      <c r="G397" s="14" t="s">
         <v>1137</v>
       </c>
-      <c r="H397" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I397" s="23" t="s">
+      <c r="H397" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I397" s="14" t="s">
         <v>1158</v>
       </c>
     </row>
     <row r="398" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A398" s="23" t="s">
+      <c r="A398" s="14" t="s">
         <v>1159</v>
       </c>
-      <c r="B398" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C398" s="23" t="s">
+      <c r="B398" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C398" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D398" s="23" t="s">
+      <c r="D398" s="14" t="s">
         <v>1152</v>
       </c>
-      <c r="E398" s="23" t="s">
+      <c r="E398" s="14" t="s">
         <v>1160</v>
       </c>
-      <c r="F398" s="23" t="s">
+      <c r="F398" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G398" s="23" t="s">
+      <c r="G398" s="14" t="s">
         <v>1161</v>
       </c>
-      <c r="H398" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I398" s="23" t="s">
+      <c r="H398" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I398" s="14" t="s">
         <v>1162</v>
       </c>
     </row>
     <row r="399" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A399" s="23" t="s">
+      <c r="A399" s="14" t="s">
         <v>1163</v>
       </c>
-      <c r="B399" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C399" s="23" t="s">
+      <c r="B399" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C399" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D399" s="23" t="s">
+      <c r="D399" s="14" t="s">
         <v>1164</v>
       </c>
-      <c r="E399" s="23" t="s">
+      <c r="E399" s="14" t="s">
         <v>1165</v>
       </c>
-      <c r="F399" s="23" t="s">
+      <c r="F399" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G399" s="23" t="s">
+      <c r="G399" s="14" t="s">
         <v>1166</v>
       </c>
-      <c r="H399" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I399" s="23" t="s">
+      <c r="H399" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I399" s="14" t="s">
         <v>1167</v>
       </c>
     </row>
     <row r="400" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A400" s="23" t="s">
+      <c r="A400" s="14" t="s">
         <v>1168</v>
       </c>
-      <c r="B400" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C400" s="23" t="s">
+      <c r="B400" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C400" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D400" s="23" t="s">
+      <c r="D400" s="14" t="s">
         <v>1169</v>
       </c>
-      <c r="E400" s="23" t="s">
+      <c r="E400" s="14" t="s">
         <v>1170</v>
       </c>
-      <c r="F400" s="23" t="s">
+      <c r="F400" s="14" t="s">
         <v>1171</v>
       </c>
-      <c r="G400" s="23" t="s">
+      <c r="G400" s="14" t="s">
         <v>1106</v>
       </c>
-      <c r="H400" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I400" s="23" t="s">
+      <c r="H400" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I400" s="14" t="s">
         <v>1172</v>
       </c>
     </row>
     <row r="401" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A401" s="23" t="s">
+      <c r="A401" s="14" t="s">
         <v>1173</v>
       </c>
-      <c r="B401" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C401" s="23" t="s">
+      <c r="B401" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C401" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D401" s="23" t="s">
+      <c r="D401" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="E401" s="23" t="s">
+      <c r="E401" s="14" t="s">
         <v>1174</v>
       </c>
-      <c r="F401" s="23" t="s">
+      <c r="F401" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="G401" s="23" t="s">
+      <c r="G401" s="14" t="s">
         <v>1089</v>
       </c>
-      <c r="H401" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I401" s="23" t="s">
+      <c r="H401" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I401" s="14" t="s">
         <v>1175</v>
       </c>
     </row>
     <row r="402" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A402" s="23" t="s">
+      <c r="A402" s="14" t="s">
         <v>1176</v>
       </c>
-      <c r="B402" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C402" s="23" t="s">
+      <c r="B402" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C402" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D402" s="23" t="s">
+      <c r="D402" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="E402" s="23" t="s">
+      <c r="E402" s="14" t="s">
         <v>1177</v>
       </c>
-      <c r="F402" s="23" t="s">
+      <c r="F402" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G402" s="23" t="s">
+      <c r="G402" s="14" t="s">
         <v>1178</v>
       </c>
-      <c r="H402" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I402" s="23" t="s">
+      <c r="H402" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I402" s="14" t="s">
         <v>1179</v>
       </c>
     </row>
     <row r="403" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A403" s="23" t="s">
+      <c r="A403" s="14" t="s">
         <v>1180</v>
       </c>
-      <c r="B403" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C403" s="23" t="s">
+      <c r="B403" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C403" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D403" s="23" t="s">
+      <c r="D403" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="E403" s="23" t="s">
+      <c r="E403" s="14" t="s">
         <v>1181</v>
       </c>
-      <c r="F403" s="23" t="s">
+      <c r="F403" s="14" t="s">
         <v>1182</v>
       </c>
-      <c r="G403" s="23" t="s">
+      <c r="G403" s="14" t="s">
         <v>1183</v>
       </c>
-      <c r="H403" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I403" s="23" t="s">
+      <c r="H403" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I403" s="14" t="s">
         <v>1184</v>
       </c>
     </row>
     <row r="404" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A404" s="23" t="s">
+      <c r="A404" s="14" t="s">
         <v>1185</v>
       </c>
-      <c r="B404" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C404" s="23" t="s">
+      <c r="B404" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C404" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D404" s="23" t="s">
+      <c r="D404" s="14" t="s">
         <v>1186</v>
       </c>
-      <c r="E404" s="23" t="s">
+      <c r="E404" s="14" t="s">
         <v>1187</v>
       </c>
-      <c r="F404" s="23" t="s">
+      <c r="F404" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G404" s="23" t="s">
+      <c r="G404" s="14" t="s">
         <v>1188</v>
       </c>
-      <c r="H404" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I404" s="23" t="s">
+      <c r="H404" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I404" s="14" t="s">
         <v>1189</v>
       </c>
     </row>
     <row r="405" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A405" s="23" t="s">
+      <c r="A405" s="14" t="s">
         <v>1190</v>
       </c>
-      <c r="B405" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C405" s="23" t="s">
+      <c r="B405" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C405" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D405" s="23" t="s">
+      <c r="D405" s="14" t="s">
         <v>1191</v>
       </c>
-      <c r="E405" s="23" t="s">
+      <c r="E405" s="14" t="s">
         <v>1192</v>
       </c>
-      <c r="F405" s="23" t="s">
+      <c r="F405" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G405" s="23" t="s">
+      <c r="G405" s="14" t="s">
         <v>1193</v>
       </c>
-      <c r="H405" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I405" s="23" t="s">
+      <c r="H405" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I405" s="14" t="s">
         <v>1194</v>
       </c>
     </row>
     <row r="406" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A406" s="23" t="s">
+      <c r="A406" s="14" t="s">
         <v>1195</v>
       </c>
-      <c r="B406" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C406" s="23" t="s">
+      <c r="B406" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C406" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D406" s="23" t="s">
+      <c r="D406" s="14" t="s">
         <v>1196</v>
       </c>
-      <c r="E406" s="23" t="s">
+      <c r="E406" s="14" t="s">
         <v>1197</v>
       </c>
-      <c r="F406" s="23" t="s">
+      <c r="F406" s="14" t="s">
         <v>1094</v>
       </c>
-      <c r="G406" s="23" t="s">
+      <c r="G406" s="14" t="s">
         <v>1198</v>
       </c>
-      <c r="H406" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I406" s="23" t="s">
+      <c r="H406" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I406" s="14" t="s">
         <v>1199</v>
       </c>
     </row>
     <row r="407" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A407" s="23" t="s">
+      <c r="A407" s="14" t="s">
         <v>1200</v>
       </c>
-      <c r="B407" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C407" s="23" t="s">
+      <c r="B407" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C407" s="14" t="s">
         <v>1087</v>
       </c>
-      <c r="D407" s="23" t="s">
+      <c r="D407" s="14" t="s">
         <v>1201</v>
       </c>
-      <c r="E407" s="23" t="s">
+      <c r="E407" s="14" t="s">
         <v>1202</v>
       </c>
-      <c r="F407" s="23" t="s">
+      <c r="F407" s="14" t="s">
         <v>1203</v>
       </c>
-      <c r="G407" s="23" t="s">
+      <c r="G407" s="14" t="s">
         <v>1089</v>
       </c>
-      <c r="H407" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="I407" s="23" t="s">
+      <c r="H407" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I407" s="14" t="s">
         <v>1204</v>
       </c>
     </row>
     <row r="409" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A409" s="28" t="s">
+      <c r="A409" s="20" t="s">
         <v>1322</v>
       </c>
-      <c r="B409" s="28"/>
+      <c r="B409" s="20"/>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A410" s="26" t="s">
+      <c r="A410" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="B410" s="26" t="s">
+      <c r="B410" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C410" s="26" t="s">
+      <c r="C410" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D410" s="26" t="s">
+      <c r="D410" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E410" s="26" t="s">
+      <c r="E410" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F410" s="26" t="s">
+      <c r="F410" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="G410" s="26" t="s">
+      <c r="G410" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="H410" s="26" t="s">
+      <c r="H410" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I410" s="26" t="s">
+      <c r="I410" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -18595,37 +18595,37 @@
       </c>
     </row>
     <row r="442" spans="1:9" ht="56" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A442" s="28" t="s">
+      <c r="A442" s="20" t="s">
         <v>1405</v>
       </c>
-      <c r="B442" s="28"/>
+      <c r="B442" s="20"/>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A443" s="26" t="s">
+      <c r="A443" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="B443" s="26" t="s">
+      <c r="B443" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C443" s="26" t="s">
+      <c r="C443" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D443" s="26" t="s">
+      <c r="D443" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E443" s="26" t="s">
+      <c r="E443" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F443" s="26" t="s">
+      <c r="F443" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="G443" s="26" t="s">
+      <c r="G443" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="H443" s="26" t="s">
+      <c r="H443" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I443" s="26" t="s">
+      <c r="I443" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -19500,37 +19500,37 @@
       </c>
     </row>
     <row r="476" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A476" s="28" t="s">
+      <c r="A476" s="20" t="s">
         <v>1450</v>
       </c>
-      <c r="B476" s="28"/>
+      <c r="B476" s="20"/>
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A477" s="26" t="s">
+      <c r="A477" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="B477" s="26" t="s">
+      <c r="B477" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C477" s="26" t="s">
+      <c r="C477" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D477" s="26" t="s">
+      <c r="D477" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E477" s="26" t="s">
+      <c r="E477" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F477" s="26" t="s">
+      <c r="F477" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="G477" s="26" t="s">
+      <c r="G477" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="H477" s="26" t="s">
+      <c r="H477" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I477" s="26" t="s">
+      <c r="I477" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -20376,37 +20376,37 @@
       </c>
     </row>
     <row r="508" spans="1:9" ht="56" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A508" s="28" t="s">
+      <c r="A508" s="20" t="s">
         <v>1494</v>
       </c>
-      <c r="B508" s="28"/>
+      <c r="B508" s="20"/>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A509" s="26" t="s">
+      <c r="A509" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="B509" s="26" t="s">
+      <c r="B509" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C509" s="26" t="s">
+      <c r="C509" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D509" s="26" t="s">
+      <c r="D509" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E509" s="26" t="s">
+      <c r="E509" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F509" s="26" t="s">
+      <c r="F509" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="G509" s="26" t="s">
+      <c r="G509" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="H509" s="26" t="s">
+      <c r="H509" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I509" s="26" t="s">
+      <c r="I509" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -21223,37 +21223,37 @@
       </c>
     </row>
     <row r="539" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A539" s="27" t="s">
+      <c r="A539" s="19" t="s">
         <v>1542</v>
       </c>
-      <c r="B539" s="27"/>
+      <c r="B539" s="19"/>
     </row>
     <row r="540" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A540" s="26" t="s">
+      <c r="A540" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="B540" s="26" t="s">
+      <c r="B540" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C540" s="26" t="s">
+      <c r="C540" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D540" s="26" t="s">
+      <c r="D540" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E540" s="26" t="s">
+      <c r="E540" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F540" s="26" t="s">
+      <c r="F540" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="G540" s="26" t="s">
+      <c r="G540" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="H540" s="26" t="s">
+      <c r="H540" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I540" s="26" t="s">
+      <c r="I540" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -22186,37 +22186,37 @@
       </c>
     </row>
     <row r="574" spans="1:9" ht="56" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A574" s="27" t="s">
+      <c r="A574" s="19" t="s">
         <v>1601</v>
       </c>
-      <c r="B574" s="27"/>
+      <c r="B574" s="19"/>
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A575" s="26" t="s">
+      <c r="A575" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="B575" s="26" t="s">
+      <c r="B575" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C575" s="26" t="s">
+      <c r="C575" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D575" s="26" t="s">
+      <c r="D575" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E575" s="26" t="s">
+      <c r="E575" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F575" s="26" t="s">
+      <c r="F575" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="G575" s="26" t="s">
+      <c r="G575" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="H575" s="26" t="s">
+      <c r="H575" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I575" s="26" t="s">
+      <c r="I575" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -23120,37 +23120,37 @@
       </c>
     </row>
     <row r="608" spans="1:9" ht="56" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A608" s="28" t="s">
+      <c r="A608" s="20" t="s">
         <v>1602</v>
       </c>
-      <c r="B608" s="28"/>
+      <c r="B608" s="20"/>
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A609" s="26" t="s">
+      <c r="A609" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="B609" s="26" t="s">
+      <c r="B609" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C609" s="26" t="s">
+      <c r="C609" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D609" s="26" t="s">
+      <c r="D609" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E609" s="26" t="s">
+      <c r="E609" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F609" s="26" t="s">
+      <c r="F609" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="G609" s="26" t="s">
+      <c r="G609" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="H609" s="26" t="s">
+      <c r="H609" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I609" s="26" t="s">
+      <c r="I609" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -24141,37 +24141,37 @@
       </c>
     </row>
     <row r="646" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A646" s="27" t="s">
+      <c r="A646" s="19" t="s">
         <v>1700</v>
       </c>
-      <c r="B646" s="27"/>
+      <c r="B646" s="19"/>
     </row>
     <row r="647" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A647" s="26" t="s">
+      <c r="A647" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="B647" s="26" t="s">
+      <c r="B647" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C647" s="26" t="s">
+      <c r="C647" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D647" s="26" t="s">
+      <c r="D647" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E647" s="26" t="s">
+      <c r="E647" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F647" s="26" t="s">
+      <c r="F647" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="G647" s="26" t="s">
+      <c r="G647" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="H647" s="26" t="s">
+      <c r="H647" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I647" s="26" t="s">
+      <c r="I647" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -25075,10 +25075,17 @@
       </c>
     </row>
     <row r="686" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A686" s="25"/>
+      <c r="A686" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A322:C322"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A161:C161"/>
+    <mergeCell ref="A204:C204"/>
+    <mergeCell ref="A267:C267"/>
     <mergeCell ref="A539:B539"/>
     <mergeCell ref="A574:B574"/>
     <mergeCell ref="A608:B608"/>
@@ -25088,13 +25095,6 @@
     <mergeCell ref="A442:B442"/>
     <mergeCell ref="A476:B476"/>
     <mergeCell ref="A508:B508"/>
-    <mergeCell ref="A322:C322"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A161:C161"/>
-    <mergeCell ref="A204:C204"/>
-    <mergeCell ref="A267:C267"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H229" r:id="rId1" xr:uid="{51F4F62C-C5AC-4C5C-9304-2B722E0CAF07}"/>
